--- a/paper-data/2026-10-21/journal.xlsx
+++ b/paper-data/2026-10-21/journal.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,94 @@
         <v>147.1014340536935</v>
       </c>
       <c r="V6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:55:33</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>221.7608</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>gap fade: gap +2.07% (open 220.96 vs prev close 216.47), first 5m bar red; target prev close</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.668</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>EOD_FLATTEN_1455</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>08:35:09</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>220.2898</v>
+      </c>
+      <c r="P7" t="n">
+        <v>222.4489</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="S7" t="n">
+        <v>381</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>221.6499938964844</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -934,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,49 +1080,6 @@
         <is>
           <t>unrealized_usd</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>08:35:09</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>220.2898</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G2" t="n">
-        <v>348.06</v>
-      </c>
-      <c r="H2" t="n">
-        <v>222.4489</v>
-      </c>
-      <c r="I2" t="n">
-        <v>216.47</v>
-      </c>
-      <c r="J2" t="n">
-        <v>219.9450073242188</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -1263,7 +1308,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1272,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.04</v>
+        <v>-12.36</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.03</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="8">
@@ -1422,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,6 +1554,106 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>984.84</v>
+      </c>
+      <c r="C4" t="n">
+        <v>636.36</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>636.36</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>982.09</v>
+      </c>
+      <c r="C6" t="n">
+        <v>636.36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>982.98</v>
+      </c>
+      <c r="C7" t="n">
+        <v>636.36</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1558,7 +1703,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30:39</t>
+          <t>2026-10-21 15:00:34</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1724,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>984.96</v>
+        <v>982.1</v>
       </c>
     </row>
     <row r="6">
@@ -1589,7 +1734,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>636.36</v>
+        <v>982.1</v>
       </c>
     </row>
     <row r="7">
@@ -1599,7 +1744,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-10.04</v>
+        <v>-12.36</v>
       </c>
     </row>
     <row r="8">
@@ -1609,7 +1754,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1619,7 +1764,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.954</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="10">
@@ -1629,7 +1774,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1659,7 +1804,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2.07</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="14">
@@ -1669,7 +1814,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
